--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>

--- a/diseases/d240/2026-2029.xlsx
+++ b/diseases/d240/2026-2029.xlsx
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -4093,6 +4093,233 @@
         </is>
       </c>
       <c r="BC16" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>viral-meningoencephalitis-surveillance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>D240</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Viral meningoencephalitis surveillance</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>病毒性脑膜脑炎监测</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_703_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Virale infeksjoner i sentralnervesystemet</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>aggregate</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>not_comparable</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_viral_CNS_aggregate</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>FHI MSIS source-defined viral central nervous system infection aggregate; component etiologies are not separable.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>no_eligible_public_projection</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>source_observations_only</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>Registered source observations are retained for provenance and downloads, but their measure is not eligible for the public cases curve.</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -4131,7 +4358,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4451,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -4244,7 +4471,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
